--- a/backend-erp/database/seeders/data/matieres_premieres.xlsx
+++ b/backend-erp/database/seeders/data/matieres_premieres.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Compagnie Malagasy de Plastique\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA531DF-6E14-40F5-B842-24E683697344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="160">
   <si>
     <t>reference</t>
   </si>
@@ -497,9 +491,6 @@
   </si>
   <si>
     <t>pcs</t>
-  </si>
-  <si>
-    <t>0.00</t>
   </si>
   <si>
     <t>seuil</t>
@@ -508,7 +499,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -558,9 +549,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -598,7 +589,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -670,7 +661,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -843,17 +834,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H73"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -873,13 +864,13 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -892,8 +883,8 @@
       <c r="E2" t="s">
         <v>157</v>
       </c>
-      <c r="F2" t="s">
-        <v>159</v>
+      <c r="F2">
+        <v>250</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -902,7 +893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -915,8 +906,8 @@
       <c r="E3" t="s">
         <v>157</v>
       </c>
-      <c r="F3" t="s">
-        <v>159</v>
+      <c r="F3">
+        <v>700</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -925,7 +916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -938,8 +929,8 @@
       <c r="E4" t="s">
         <v>157</v>
       </c>
-      <c r="F4" t="s">
-        <v>159</v>
+      <c r="F4">
+        <v>850</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -948,7 +939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -961,8 +952,8 @@
       <c r="E5" t="s">
         <v>157</v>
       </c>
-      <c r="F5" t="s">
-        <v>159</v>
+      <c r="F5">
+        <v>250</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -971,7 +962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -984,8 +975,8 @@
       <c r="E6" t="s">
         <v>157</v>
       </c>
-      <c r="F6" t="s">
-        <v>159</v>
+      <c r="F6">
+        <v>740</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -994,7 +985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1007,8 +998,8 @@
       <c r="E7" t="s">
         <v>157</v>
       </c>
-      <c r="F7" t="s">
-        <v>159</v>
+      <c r="F7">
+        <v>300</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1017,7 +1008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1030,8 +1021,8 @@
       <c r="E8" t="s">
         <v>157</v>
       </c>
-      <c r="F8" t="s">
-        <v>159</v>
+      <c r="F8">
+        <v>250</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1040,7 +1031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1053,8 +1044,8 @@
       <c r="E9" t="s">
         <v>157</v>
       </c>
-      <c r="F9" t="s">
-        <v>159</v>
+      <c r="F9">
+        <v>260</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1063,7 +1054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1076,8 +1067,8 @@
       <c r="E10" t="s">
         <v>157</v>
       </c>
-      <c r="F10" t="s">
-        <v>159</v>
+      <c r="F10">
+        <v>250</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1086,7 +1077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1099,8 +1090,8 @@
       <c r="E11" t="s">
         <v>157</v>
       </c>
-      <c r="F11" t="s">
-        <v>159</v>
+      <c r="F11">
+        <v>250</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1109,7 +1100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1122,8 +1113,8 @@
       <c r="E12" t="s">
         <v>157</v>
       </c>
-      <c r="F12" t="s">
-        <v>159</v>
+      <c r="F12">
+        <v>250</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1132,7 +1123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1145,8 +1136,8 @@
       <c r="E13" t="s">
         <v>157</v>
       </c>
-      <c r="F13" t="s">
-        <v>159</v>
+      <c r="F13">
+        <v>250</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1155,7 +1146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1168,8 +1159,8 @@
       <c r="E14" t="s">
         <v>157</v>
       </c>
-      <c r="F14" t="s">
-        <v>159</v>
+      <c r="F14">
+        <v>250</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1178,7 +1169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -1191,8 +1182,8 @@
       <c r="E15" t="s">
         <v>157</v>
       </c>
-      <c r="F15" t="s">
-        <v>159</v>
+      <c r="F15">
+        <v>250</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1201,7 +1192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1214,8 +1205,8 @@
       <c r="E16" t="s">
         <v>157</v>
       </c>
-      <c r="F16" t="s">
-        <v>159</v>
+      <c r="F16">
+        <v>250</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1224,7 +1215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -1237,8 +1228,8 @@
       <c r="E17" t="s">
         <v>157</v>
       </c>
-      <c r="F17" t="s">
-        <v>159</v>
+      <c r="F17">
+        <v>250</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1247,7 +1238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1260,8 +1251,8 @@
       <c r="E18" t="s">
         <v>157</v>
       </c>
-      <c r="F18" t="s">
-        <v>159</v>
+      <c r="F18">
+        <v>250</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1270,7 +1261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1283,8 +1274,8 @@
       <c r="E19" t="s">
         <v>157</v>
       </c>
-      <c r="F19" t="s">
-        <v>159</v>
+      <c r="F19">
+        <v>250</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1293,7 +1284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1306,8 +1297,8 @@
       <c r="E20" t="s">
         <v>157</v>
       </c>
-      <c r="F20" t="s">
-        <v>159</v>
+      <c r="F20">
+        <v>250</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1316,7 +1307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -1329,8 +1320,8 @@
       <c r="E21" t="s">
         <v>157</v>
       </c>
-      <c r="F21" t="s">
-        <v>159</v>
+      <c r="F21">
+        <v>250</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1339,7 +1330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -1352,8 +1343,8 @@
       <c r="E22" t="s">
         <v>157</v>
       </c>
-      <c r="F22" t="s">
-        <v>159</v>
+      <c r="F22">
+        <v>250</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1362,7 +1353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -1375,8 +1366,8 @@
       <c r="E23" t="s">
         <v>157</v>
       </c>
-      <c r="F23" t="s">
-        <v>159</v>
+      <c r="F23">
+        <v>250</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1385,7 +1376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1398,8 +1389,8 @@
       <c r="E24" t="s">
         <v>157</v>
       </c>
-      <c r="F24" t="s">
-        <v>159</v>
+      <c r="F24">
+        <v>250</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1408,7 +1399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1421,8 +1412,8 @@
       <c r="E25" t="s">
         <v>157</v>
       </c>
-      <c r="F25" t="s">
-        <v>159</v>
+      <c r="F25">
+        <v>250</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1431,7 +1422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -1444,8 +1435,8 @@
       <c r="E26" t="s">
         <v>157</v>
       </c>
-      <c r="F26" t="s">
-        <v>159</v>
+      <c r="F26">
+        <v>250</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1454,7 +1445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1467,8 +1458,8 @@
       <c r="E27" t="s">
         <v>157</v>
       </c>
-      <c r="F27" t="s">
-        <v>159</v>
+      <c r="F27">
+        <v>250</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1477,7 +1468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -1490,8 +1481,8 @@
       <c r="E28" t="s">
         <v>157</v>
       </c>
-      <c r="F28" t="s">
-        <v>159</v>
+      <c r="F28">
+        <v>250</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -1500,7 +1491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -1513,8 +1504,8 @@
       <c r="E29" t="s">
         <v>157</v>
       </c>
-      <c r="F29" t="s">
-        <v>159</v>
+      <c r="F29">
+        <v>250</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1523,7 +1514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -1536,8 +1527,8 @@
       <c r="E30" t="s">
         <v>157</v>
       </c>
-      <c r="F30" t="s">
-        <v>159</v>
+      <c r="F30">
+        <v>250</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -1546,7 +1537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -1559,8 +1550,8 @@
       <c r="E31" t="s">
         <v>157</v>
       </c>
-      <c r="F31" t="s">
-        <v>159</v>
+      <c r="F31">
+        <v>250</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -1569,7 +1560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -1582,8 +1573,8 @@
       <c r="E32" t="s">
         <v>157</v>
       </c>
-      <c r="F32" t="s">
-        <v>159</v>
+      <c r="F32">
+        <v>250</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1592,7 +1583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -1605,8 +1596,8 @@
       <c r="E33" t="s">
         <v>157</v>
       </c>
-      <c r="F33" t="s">
-        <v>159</v>
+      <c r="F33">
+        <v>250</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -1615,7 +1606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -1628,8 +1619,8 @@
       <c r="E34" t="s">
         <v>157</v>
       </c>
-      <c r="F34" t="s">
-        <v>159</v>
+      <c r="F34">
+        <v>250</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -1638,7 +1629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -1651,8 +1642,8 @@
       <c r="E35" t="s">
         <v>157</v>
       </c>
-      <c r="F35" t="s">
-        <v>159</v>
+      <c r="F35">
+        <v>250</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -1661,7 +1652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -1674,8 +1665,8 @@
       <c r="E36" t="s">
         <v>157</v>
       </c>
-      <c r="F36" t="s">
-        <v>159</v>
+      <c r="F36">
+        <v>250</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -1684,7 +1675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -1697,8 +1688,8 @@
       <c r="E37" t="s">
         <v>157</v>
       </c>
-      <c r="F37" t="s">
-        <v>159</v>
+      <c r="F37">
+        <v>250</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -1707,7 +1698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -1720,8 +1711,8 @@
       <c r="E38" t="s">
         <v>157</v>
       </c>
-      <c r="F38" t="s">
-        <v>159</v>
+      <c r="F38">
+        <v>250</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -1730,7 +1721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -1743,8 +1734,8 @@
       <c r="E39" t="s">
         <v>157</v>
       </c>
-      <c r="F39" t="s">
-        <v>159</v>
+      <c r="F39">
+        <v>250</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -1753,7 +1744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -1766,8 +1757,8 @@
       <c r="E40" t="s">
         <v>157</v>
       </c>
-      <c r="F40" t="s">
-        <v>159</v>
+      <c r="F40">
+        <v>250</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -1776,7 +1767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -1789,8 +1780,8 @@
       <c r="E41" t="s">
         <v>157</v>
       </c>
-      <c r="F41" t="s">
-        <v>159</v>
+      <c r="F41">
+        <v>250</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -1799,7 +1790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -1812,8 +1803,8 @@
       <c r="E42" t="s">
         <v>157</v>
       </c>
-      <c r="F42" t="s">
-        <v>159</v>
+      <c r="F42">
+        <v>250</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -1822,7 +1813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -1835,8 +1826,8 @@
       <c r="E43" t="s">
         <v>157</v>
       </c>
-      <c r="F43" t="s">
-        <v>159</v>
+      <c r="F43">
+        <v>250</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -1845,7 +1836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1858,8 +1849,8 @@
       <c r="E44" t="s">
         <v>157</v>
       </c>
-      <c r="F44" t="s">
-        <v>159</v>
+      <c r="F44">
+        <v>250</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -1868,7 +1859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1881,8 +1872,8 @@
       <c r="E45" t="s">
         <v>157</v>
       </c>
-      <c r="F45" t="s">
-        <v>159</v>
+      <c r="F45">
+        <v>250</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -1891,7 +1882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1904,8 +1895,8 @@
       <c r="E46" t="s">
         <v>157</v>
       </c>
-      <c r="F46" t="s">
-        <v>159</v>
+      <c r="F46">
+        <v>250</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -1914,7 +1905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1927,8 +1918,8 @@
       <c r="E47" t="s">
         <v>157</v>
       </c>
-      <c r="F47" t="s">
-        <v>159</v>
+      <c r="F47">
+        <v>250</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -1937,7 +1928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -1950,8 +1941,8 @@
       <c r="E48" t="s">
         <v>157</v>
       </c>
-      <c r="F48" t="s">
-        <v>159</v>
+      <c r="F48">
+        <v>250</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -1960,7 +1951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -1973,8 +1964,8 @@
       <c r="E49" t="s">
         <v>157</v>
       </c>
-      <c r="F49" t="s">
-        <v>159</v>
+      <c r="F49">
+        <v>250</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -1983,7 +1974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -1996,8 +1987,8 @@
       <c r="E50" t="s">
         <v>157</v>
       </c>
-      <c r="F50" t="s">
-        <v>159</v>
+      <c r="F50">
+        <v>250</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -2006,7 +1997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -2019,8 +2010,8 @@
       <c r="E51" t="s">
         <v>157</v>
       </c>
-      <c r="F51" t="s">
-        <v>159</v>
+      <c r="F51">
+        <v>250</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2029,7 +2020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -2042,8 +2033,8 @@
       <c r="E52" t="s">
         <v>157</v>
       </c>
-      <c r="F52" t="s">
-        <v>159</v>
+      <c r="F52">
+        <v>250</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2052,7 +2043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -2065,8 +2056,8 @@
       <c r="E53" t="s">
         <v>157</v>
       </c>
-      <c r="F53" t="s">
-        <v>159</v>
+      <c r="F53">
+        <v>250</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2075,7 +2066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>59</v>
       </c>
@@ -2088,8 +2079,8 @@
       <c r="E54" t="s">
         <v>157</v>
       </c>
-      <c r="F54" t="s">
-        <v>159</v>
+      <c r="F54">
+        <v>250</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -2098,7 +2089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>60</v>
       </c>
@@ -2111,8 +2102,8 @@
       <c r="E55" t="s">
         <v>158</v>
       </c>
-      <c r="F55" t="s">
-        <v>159</v>
+      <c r="F55">
+        <v>250</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -2121,7 +2112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -2134,8 +2125,8 @@
       <c r="E56" t="s">
         <v>157</v>
       </c>
-      <c r="F56" t="s">
-        <v>159</v>
+      <c r="F56">
+        <v>250</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -2144,7 +2135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -2157,8 +2148,8 @@
       <c r="E57" t="s">
         <v>157</v>
       </c>
-      <c r="F57" t="s">
-        <v>159</v>
+      <c r="F57">
+        <v>250</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -2167,7 +2158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -2180,8 +2171,8 @@
       <c r="E58" t="s">
         <v>157</v>
       </c>
-      <c r="F58" t="s">
-        <v>159</v>
+      <c r="F58">
+        <v>250</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -2190,7 +2181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -2203,8 +2194,8 @@
       <c r="E59" t="s">
         <v>157</v>
       </c>
-      <c r="F59" t="s">
-        <v>159</v>
+      <c r="F59">
+        <v>250</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -2213,7 +2204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -2226,8 +2217,8 @@
       <c r="E60" t="s">
         <v>157</v>
       </c>
-      <c r="F60" t="s">
-        <v>159</v>
+      <c r="F60">
+        <v>250</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -2236,7 +2227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -2249,8 +2240,8 @@
       <c r="E61" t="s">
         <v>157</v>
       </c>
-      <c r="F61" t="s">
-        <v>159</v>
+      <c r="F61">
+        <v>250</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -2259,7 +2250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>67</v>
       </c>
@@ -2272,8 +2263,8 @@
       <c r="E62" t="s">
         <v>157</v>
       </c>
-      <c r="F62" t="s">
-        <v>159</v>
+      <c r="F62">
+        <v>250</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -2282,7 +2273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -2295,8 +2286,8 @@
       <c r="E63" t="s">
         <v>157</v>
       </c>
-      <c r="F63" t="s">
-        <v>159</v>
+      <c r="F63">
+        <v>250</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -2305,7 +2296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -2318,8 +2309,8 @@
       <c r="E64" t="s">
         <v>157</v>
       </c>
-      <c r="F64" t="s">
-        <v>159</v>
+      <c r="F64">
+        <v>250</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -2328,7 +2319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>70</v>
       </c>
@@ -2341,8 +2332,8 @@
       <c r="E65" t="s">
         <v>157</v>
       </c>
-      <c r="F65" t="s">
-        <v>159</v>
+      <c r="F65">
+        <v>250</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -2351,7 +2342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>71</v>
       </c>
@@ -2364,8 +2355,8 @@
       <c r="E66" t="s">
         <v>157</v>
       </c>
-      <c r="F66" t="s">
-        <v>159</v>
+      <c r="F66">
+        <v>250</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -2374,7 +2365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>72</v>
       </c>
@@ -2387,8 +2378,8 @@
       <c r="E67" t="s">
         <v>157</v>
       </c>
-      <c r="F67" t="s">
-        <v>159</v>
+      <c r="F67">
+        <v>250</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -2397,7 +2388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>73</v>
       </c>
@@ -2410,8 +2401,8 @@
       <c r="E68" t="s">
         <v>157</v>
       </c>
-      <c r="F68" t="s">
-        <v>159</v>
+      <c r="F68">
+        <v>250</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -2420,7 +2411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>74</v>
       </c>
@@ -2433,8 +2424,8 @@
       <c r="E69" t="s">
         <v>158</v>
       </c>
-      <c r="F69" t="s">
-        <v>159</v>
+      <c r="F69">
+        <v>250</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -2443,7 +2434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>75</v>
       </c>
@@ -2456,8 +2447,8 @@
       <c r="E70" t="s">
         <v>157</v>
       </c>
-      <c r="F70" t="s">
-        <v>159</v>
+      <c r="F70">
+        <v>250</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -2466,7 +2457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>76</v>
       </c>
@@ -2479,8 +2470,8 @@
       <c r="E71" t="s">
         <v>157</v>
       </c>
-      <c r="F71" t="s">
-        <v>159</v>
+      <c r="F71">
+        <v>250</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -2489,7 +2480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>77</v>
       </c>
@@ -2502,8 +2493,8 @@
       <c r="E72" t="s">
         <v>157</v>
       </c>
-      <c r="F72" t="s">
-        <v>159</v>
+      <c r="F72">
+        <v>250</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -2512,7 +2503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>78</v>
       </c>
@@ -2525,8 +2516,8 @@
       <c r="E73" t="s">
         <v>157</v>
       </c>
-      <c r="F73" t="s">
-        <v>159</v>
+      <c r="F73">
+        <v>250</v>
       </c>
       <c r="G73">
         <v>0</v>
